--- a/artfynd/A 41592-2024 artfynd.xlsx
+++ b/artfynd/A 41592-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,6 +795,764 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123301028</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>S. Skorvtjärnshöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>618450</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6969876</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123301020</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79355</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>S. Skorvtjärnshöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>618478</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6969975</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123301027</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>S. Skorvtjärnshöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>618447</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6969868</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>859</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123301024</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>S. Skorvtjärnshöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>618458</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6969961</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123301023</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>S. Skorvtjärnshöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>618485</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6969922</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123301029</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79876</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>S. Skorvtjärnshöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>618473</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6969856</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>på sälg i fuktdråg</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linnéa Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 41592-2024 artfynd.xlsx
+++ b/artfynd/A 41592-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123301028</v>
+        <v>123301023</v>
       </c>
       <c r="B3" t="n">
-        <v>90952</v>
+        <v>78769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,43 +816,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618450</v>
+        <v>618485</v>
       </c>
       <c r="R3" t="n">
-        <v>6969876</v>
+        <v>6969922</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +870,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +910,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -933,7 +924,7 @@
         <v>123301020</v>
       </c>
       <c r="B4" t="n">
-        <v>79355</v>
+        <v>79358</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1051,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123301027</v>
+        <v>123301028</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1100,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618447</v>
+        <v>618450</v>
       </c>
       <c r="R5" t="n">
-        <v>6969868</v>
+        <v>6969876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1121,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1140,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1150,7 +1141,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,7 +1175,7 @@
         <v>123301024</v>
       </c>
       <c r="B6" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1311,10 +1302,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123301023</v>
+        <v>123301027</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>90955</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1327,34 +1318,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618485</v>
+        <v>618447</v>
       </c>
       <c r="R7" t="n">
-        <v>6969922</v>
+        <v>6969868</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>859</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1435,7 +1435,7 @@
         <v>123301029</v>
       </c>
       <c r="B8" t="n">
-        <v>79876</v>
+        <v>79879</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 41592-2024 artfynd.xlsx
+++ b/artfynd/A 41592-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123301023</v>
+        <v>123301028</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>90957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,34 +816,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618485</v>
+        <v>618450</v>
       </c>
       <c r="R3" t="n">
-        <v>6969922</v>
+        <v>6969876</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -880,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -924,7 +933,7 @@
         <v>123301020</v>
       </c>
       <c r="B4" t="n">
-        <v>79358</v>
+        <v>79360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1042,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123301028</v>
+        <v>123301027</v>
       </c>
       <c r="B5" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,10 +1100,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618450</v>
+        <v>618447</v>
       </c>
       <c r="R5" t="n">
-        <v>6969876</v>
+        <v>6969868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1130,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>859</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1131,7 +1140,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,7 +1150,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,7 +1170,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1175,7 +1184,7 @@
         <v>123301024</v>
       </c>
       <c r="B6" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1302,10 +1311,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123301027</v>
+        <v>123301023</v>
       </c>
       <c r="B7" t="n">
-        <v>90955</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1318,43 +1327,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618447</v>
+        <v>618485</v>
       </c>
       <c r="R7" t="n">
-        <v>6969868</v>
+        <v>6969922</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1435,7 +1435,7 @@
         <v>123301029</v>
       </c>
       <c r="B8" t="n">
-        <v>79879</v>
+        <v>79881</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 41592-2024 artfynd.xlsx
+++ b/artfynd/A 41592-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>123301028</v>
       </c>
       <c r="B3" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>123301020</v>
       </c>
       <c r="B4" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>123301027</v>
       </c>
       <c r="B5" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1181,10 +1181,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123301024</v>
+        <v>123301023</v>
       </c>
       <c r="B6" t="n">
-        <v>90957</v>
+        <v>78772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1197,43 +1197,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618458</v>
+        <v>618485</v>
       </c>
       <c r="R6" t="n">
-        <v>6969961</v>
+        <v>6969922</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,7 +1251,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1270,7 +1261,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1280,7 +1271,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1291,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1311,10 +1302,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123301023</v>
+        <v>123301029</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>79882</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,25 +1314,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1351,10 +1342,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618485</v>
+        <v>618473</v>
       </c>
       <c r="R7" t="n">
-        <v>6969922</v>
+        <v>6969856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1381,7 +1372,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>857</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1391,7 +1382,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1401,7 +1392,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>på sälg i fuktdråg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,7 +1417,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1432,10 +1428,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123301029</v>
+        <v>123301024</v>
       </c>
       <c r="B8" t="n">
-        <v>79881</v>
+        <v>90963</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1444,38 +1440,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618473</v>
+        <v>618458</v>
       </c>
       <c r="R8" t="n">
-        <v>6969856</v>
+        <v>6969961</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1502,7 +1507,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1512,7 +1517,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1522,12 +1527,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>på sälg i fuktdråg</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 41592-2024 artfynd.xlsx
+++ b/artfynd/A 41592-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123301028</v>
+        <v>123301020</v>
       </c>
       <c r="B3" t="n">
-        <v>90963</v>
+        <v>79364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,43 +816,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618450</v>
+        <v>618478</v>
       </c>
       <c r="R3" t="n">
-        <v>6969876</v>
+        <v>6969975</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +870,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>866</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123301020</v>
+        <v>123301024</v>
       </c>
       <c r="B4" t="n">
-        <v>79361</v>
+        <v>90966</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,34 +937,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618478</v>
+        <v>618458</v>
       </c>
       <c r="R4" t="n">
-        <v>6969975</v>
+        <v>6969961</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123301027</v>
+        <v>123301028</v>
       </c>
       <c r="B5" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618447</v>
+        <v>618450</v>
       </c>
       <c r="R5" t="n">
-        <v>6969868</v>
+        <v>6969876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,7 +1184,7 @@
         <v>123301023</v>
       </c>
       <c r="B6" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123301029</v>
+        <v>123301027</v>
       </c>
       <c r="B7" t="n">
-        <v>79882</v>
+        <v>90966</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,38 +1314,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618473</v>
+        <v>618447</v>
       </c>
       <c r="R7" t="n">
-        <v>6969856</v>
+        <v>6969868</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,7 +1381,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>859</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1382,7 +1391,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1392,12 +1401,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>på sälg i fuktdråg</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,7 +1421,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1428,10 +1432,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123301024</v>
+        <v>123301029</v>
       </c>
       <c r="B8" t="n">
-        <v>90963</v>
+        <v>79885</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1440,47 +1444,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618458</v>
+        <v>618473</v>
       </c>
       <c r="R8" t="n">
-        <v>6969961</v>
+        <v>6969856</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1507,7 +1502,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>857</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1517,7 +1512,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1527,7 +1522,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>på sälg i fuktdråg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 41592-2024 artfynd.xlsx
+++ b/artfynd/A 41592-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>123301020</v>
       </c>
       <c r="B3" t="n">
-        <v>79364</v>
+        <v>79370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -921,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123301024</v>
+        <v>123301027</v>
       </c>
       <c r="B4" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618458</v>
+        <v>618447</v>
       </c>
       <c r="R4" t="n">
-        <v>6969961</v>
+        <v>6969868</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>859</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
         <v>123301028</v>
       </c>
       <c r="B5" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1181,10 +1181,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123301023</v>
+        <v>123301024</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
+        <v>90983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1197,34 +1197,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618485</v>
+        <v>618458</v>
       </c>
       <c r="R6" t="n">
-        <v>6969922</v>
+        <v>6969961</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1251,7 +1260,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1261,7 +1270,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1271,7 +1280,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,7 +1300,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1302,10 +1311,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123301027</v>
+        <v>123301029</v>
       </c>
       <c r="B7" t="n">
-        <v>90966</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,47 +1323,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618447</v>
+        <v>618473</v>
       </c>
       <c r="R7" t="n">
-        <v>6969868</v>
+        <v>6969856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>857</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1401,7 +1401,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>på sälg i fuktdråg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,7 +1426,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1432,10 +1437,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123301029</v>
+        <v>123301023</v>
       </c>
       <c r="B8" t="n">
-        <v>79885</v>
+        <v>78781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1444,25 +1449,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1472,10 +1477,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618473</v>
+        <v>618485</v>
       </c>
       <c r="R8" t="n">
-        <v>6969856</v>
+        <v>6969922</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1502,7 +1507,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1512,7 +1517,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1522,12 +1527,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>på sälg i fuktdråg</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 41592-2024 artfynd.xlsx
+++ b/artfynd/A 41592-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123301020</v>
+        <v>123301024</v>
       </c>
       <c r="B3" t="n">
-        <v>79370</v>
+        <v>90988</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,34 +816,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618478</v>
+        <v>618458</v>
       </c>
       <c r="R3" t="n">
-        <v>6969975</v>
+        <v>6969961</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -880,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123301027</v>
+        <v>123301028</v>
       </c>
       <c r="B4" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618447</v>
+        <v>618450</v>
       </c>
       <c r="R4" t="n">
-        <v>6969868</v>
+        <v>6969876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1010,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123301028</v>
+        <v>123301023</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,43 +1076,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618450</v>
+        <v>618485</v>
       </c>
       <c r="R5" t="n">
-        <v>6969876</v>
+        <v>6969922</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1181,10 +1181,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123301024</v>
+        <v>123301027</v>
       </c>
       <c r="B6" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618458</v>
+        <v>618447</v>
       </c>
       <c r="R6" t="n">
-        <v>6969961</v>
+        <v>6969868</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>859</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,7 +1314,7 @@
         <v>123301029</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>79896</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123301023</v>
+        <v>123301020</v>
       </c>
       <c r="B8" t="n">
-        <v>78781</v>
+        <v>79375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1453,21 +1453,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618485</v>
+        <v>618478</v>
       </c>
       <c r="R8" t="n">
-        <v>6969922</v>
+        <v>6969975</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>866</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 41592-2024 artfynd.xlsx
+++ b/artfynd/A 41592-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>123301024</v>
       </c>
       <c r="B3" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>123301028</v>
       </c>
       <c r="B4" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123301023</v>
+        <v>123301020</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>79377</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,21 +1076,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618485</v>
+        <v>618478</v>
       </c>
       <c r="R5" t="n">
-        <v>6969922</v>
+        <v>6969975</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>866</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1184,7 +1184,7 @@
         <v>123301027</v>
       </c>
       <c r="B6" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123301029</v>
+        <v>123301023</v>
       </c>
       <c r="B7" t="n">
-        <v>79896</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618473</v>
+        <v>618485</v>
       </c>
       <c r="R7" t="n">
-        <v>6969856</v>
+        <v>6969922</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1401,12 +1401,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>på sälg i fuktdråg</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1426,7 +1421,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1437,10 +1432,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123301020</v>
+        <v>123301029</v>
       </c>
       <c r="B8" t="n">
-        <v>79375</v>
+        <v>79898</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1449,25 +1444,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1477,10 +1472,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618478</v>
+        <v>618473</v>
       </c>
       <c r="R8" t="n">
-        <v>6969975</v>
+        <v>6969856</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1507,7 +1502,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>857</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1517,7 +1512,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1527,7 +1522,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>på sälg i fuktdråg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 41592-2024 artfynd.xlsx
+++ b/artfynd/A 41592-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123301024</v>
+        <v>123301020</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>79377</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,43 +816,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618458</v>
+        <v>618478</v>
       </c>
       <c r="R3" t="n">
-        <v>6969961</v>
+        <v>6969975</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +870,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>866</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123301028</v>
+        <v>123301029</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
+        <v>79898</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,47 +933,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618450</v>
+        <v>618473</v>
       </c>
       <c r="R4" t="n">
-        <v>6969876</v>
+        <v>6969856</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +991,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>857</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1011,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på sälg i fuktdråg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,7 +1036,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1060,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123301020</v>
+        <v>123301024</v>
       </c>
       <c r="B5" t="n">
-        <v>79377</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,34 +1063,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618478</v>
+        <v>618458</v>
       </c>
       <c r="R5" t="n">
-        <v>6969975</v>
+        <v>6969961</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1126,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1140,7 +1136,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1150,7 +1146,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1177,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123301027</v>
+        <v>123301028</v>
       </c>
       <c r="B6" t="n">
         <v>90990</v>
@@ -1230,10 +1226,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618447</v>
+        <v>618450</v>
       </c>
       <c r="R6" t="n">
-        <v>6969868</v>
+        <v>6969876</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,7 +1256,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1270,7 +1266,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1280,7 +1276,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1296,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1432,10 +1428,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123301029</v>
+        <v>123301027</v>
       </c>
       <c r="B8" t="n">
-        <v>79898</v>
+        <v>90990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1444,38 +1440,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618473</v>
+        <v>618447</v>
       </c>
       <c r="R8" t="n">
-        <v>6969856</v>
+        <v>6969868</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1502,7 +1507,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>859</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1512,7 +1517,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1522,12 +1527,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>på sälg i fuktdråg</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 41592-2024 artfynd.xlsx
+++ b/artfynd/A 41592-2024 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123301023</v>
+        <v>123301027</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,34 +1323,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618485</v>
+        <v>618447</v>
       </c>
       <c r="R7" t="n">
-        <v>6969922</v>
+        <v>6969868</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,7 +1386,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>859</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1387,7 +1396,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1397,7 +1406,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,7 +1426,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1428,10 +1437,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123301027</v>
+        <v>123301023</v>
       </c>
       <c r="B8" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1444,43 +1453,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618447</v>
+        <v>618485</v>
       </c>
       <c r="R8" t="n">
-        <v>6969868</v>
+        <v>6969922</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 41592-2024 artfynd.xlsx
+++ b/artfynd/A 41592-2024 artfynd.xlsx
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123301024</v>
+        <v>123301023</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,43 +1063,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618458</v>
+        <v>618485</v>
       </c>
       <c r="R5" t="n">
-        <v>6969961</v>
+        <v>6969922</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1117,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1136,7 +1127,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1146,7 +1137,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,7 +1157,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1177,7 +1168,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123301028</v>
+        <v>123301024</v>
       </c>
       <c r="B6" t="n">
         <v>90990</v>
@@ -1226,10 +1217,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618450</v>
+        <v>618458</v>
       </c>
       <c r="R6" t="n">
-        <v>6969876</v>
+        <v>6969961</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,7 +1247,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1266,7 +1257,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1276,7 +1267,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,7 +1298,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123301027</v>
+        <v>123301028</v>
       </c>
       <c r="B7" t="n">
         <v>90990</v>
@@ -1356,10 +1347,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618447</v>
+        <v>618450</v>
       </c>
       <c r="R7" t="n">
-        <v>6969868</v>
+        <v>6969876</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1386,7 +1377,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1396,7 +1387,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1406,7 +1397,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1437,10 +1428,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123301023</v>
+        <v>123301027</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1453,34 +1444,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618485</v>
+        <v>618447</v>
       </c>
       <c r="R8" t="n">
-        <v>6969922</v>
+        <v>6969868</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>859</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 41592-2024 artfynd.xlsx
+++ b/artfynd/A 41592-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123301020</v>
+        <v>123301027</v>
       </c>
       <c r="B3" t="n">
-        <v>79377</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,34 +816,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618478</v>
+        <v>618447</v>
       </c>
       <c r="R3" t="n">
-        <v>6969975</v>
+        <v>6969868</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>859</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -880,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123301029</v>
+        <v>123301024</v>
       </c>
       <c r="B4" t="n">
-        <v>79898</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,38 +942,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618473</v>
+        <v>618458</v>
       </c>
       <c r="R4" t="n">
-        <v>6969856</v>
+        <v>6969961</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1001,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,12 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>på sälg i fuktdråg</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,7 +1049,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1047,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123301023</v>
+        <v>123301028</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,34 +1076,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618485</v>
+        <v>618450</v>
       </c>
       <c r="R5" t="n">
-        <v>6969922</v>
+        <v>6969876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1139,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1127,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1137,7 +1159,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,7 +1179,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1168,10 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123301024</v>
+        <v>123301029</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
+        <v>79898</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,47 +1202,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618458</v>
+        <v>618473</v>
       </c>
       <c r="R6" t="n">
-        <v>6969961</v>
+        <v>6969856</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,7 +1260,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>857</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1257,7 +1270,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1267,7 +1280,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på sälg i fuktdråg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,7 +1305,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1298,10 +1316,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123301028</v>
+        <v>123301020</v>
       </c>
       <c r="B7" t="n">
-        <v>90990</v>
+        <v>79377</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,43 +1332,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618450</v>
+        <v>618478</v>
       </c>
       <c r="R7" t="n">
-        <v>6969876</v>
+        <v>6969975</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,7 +1386,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>866</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1387,7 +1396,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1397,7 +1406,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1428,10 +1437,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123301027</v>
+        <v>123301023</v>
       </c>
       <c r="B8" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1444,43 +1453,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618447</v>
+        <v>618485</v>
       </c>
       <c r="R8" t="n">
-        <v>6969868</v>
+        <v>6969922</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 41592-2024 artfynd.xlsx
+++ b/artfynd/A 41592-2024 artfynd.xlsx
@@ -1060,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123301028</v>
+        <v>123301023</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,43 +1076,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618450</v>
+        <v>618485</v>
       </c>
       <c r="R5" t="n">
-        <v>6969876</v>
+        <v>6969922</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,7 +1130,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1149,7 +1140,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,7 +1150,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,7 +1170,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1190,10 +1181,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123301029</v>
+        <v>123301020</v>
       </c>
       <c r="B6" t="n">
-        <v>79898</v>
+        <v>79377</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1202,25 +1193,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1230,10 +1221,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618473</v>
+        <v>618478</v>
       </c>
       <c r="R6" t="n">
-        <v>6969856</v>
+        <v>6969975</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,7 +1251,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>866</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1270,7 +1261,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1280,12 +1271,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på sälg i fuktdråg</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,7 +1291,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1316,10 +1302,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123301020</v>
+        <v>123301029</v>
       </c>
       <c r="B7" t="n">
-        <v>79377</v>
+        <v>79898</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1328,25 +1314,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1356,10 +1342,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618478</v>
+        <v>618473</v>
       </c>
       <c r="R7" t="n">
-        <v>6969975</v>
+        <v>6969856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1386,7 +1372,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>857</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1396,7 +1382,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1406,7 +1392,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>på sälg i fuktdråg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1426,7 +1417,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1437,10 +1428,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123301023</v>
+        <v>123301028</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1453,34 +1444,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>S. Skorvtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618485</v>
+        <v>618450</v>
       </c>
       <c r="R8" t="n">
-        <v>6969922</v>
+        <v>6969876</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 41592-2024 artfynd.xlsx
+++ b/artfynd/A 41592-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301024</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301027</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301028</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1163,6 +1183,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301023</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1284,6 +1309,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301029</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1400,8 +1430,21 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301020</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>